--- a/2-EXCEL/validacao_temporal_2026-01-01.xlsx
+++ b/2-EXCEL/validacao_temporal_2026-01-01.xlsx
@@ -479,10 +479,10 @@
         <v>80.0%</v>
       </c>
       <c r="J2" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K2" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="3">
@@ -514,10 +514,10 @@
         <v>40.0%</v>
       </c>
       <c r="J3" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K3" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         <v>80.0%</v>
       </c>
       <c r="J4" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K4" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="5">
@@ -584,10 +584,10 @@
         <v>80.0%</v>
       </c>
       <c r="J5" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K5" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="6">
@@ -622,7 +622,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K6" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="7">
@@ -654,10 +654,10 @@
         <v>60.0%</v>
       </c>
       <c r="J7" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K7" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K9" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="10">
@@ -762,7 +762,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K10" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="11">
@@ -797,7 +797,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K11" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="12">
@@ -867,7 +867,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K13" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="14">
@@ -899,10 +899,10 @@
         <v>60.0%</v>
       </c>
       <c r="J14" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K14" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="15">
@@ -934,10 +934,10 @@
         <v>60.0%</v>
       </c>
       <c r="J15" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K15" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="16">
@@ -972,7 +972,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K16" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="17">
@@ -1004,10 +1004,10 @@
         <v>60.0%</v>
       </c>
       <c r="J17" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K17" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="18">
@@ -1077,7 +1077,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K19" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="20">
@@ -1112,7 +1112,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K20" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="21">
@@ -1147,7 +1147,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K21" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="22">
@@ -1217,7 +1217,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K23" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="24">
@@ -1249,10 +1249,10 @@
         <v>40.0%</v>
       </c>
       <c r="J24" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K24" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="25">
@@ -1284,10 +1284,10 @@
         <v>20.0%</v>
       </c>
       <c r="J25" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K25" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="26">
@@ -1322,7 +1322,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K26" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="27">
@@ -1354,10 +1354,10 @@
         <v>40.0%</v>
       </c>
       <c r="J27" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K27" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="28">
@@ -1427,7 +1427,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K29" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="30">
@@ -1462,7 +1462,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K30" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="31">
@@ -1497,7 +1497,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K31" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="32">
@@ -1567,7 +1567,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K33" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="34">
@@ -1599,10 +1599,10 @@
         <v>80.0%</v>
       </c>
       <c r="J34" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K34" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="35">
@@ -1634,10 +1634,10 @@
         <v>80.0%</v>
       </c>
       <c r="J35" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K35" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="36">
@@ -1672,7 +1672,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K36" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="37">
@@ -1704,10 +1704,10 @@
         <v>20.0%</v>
       </c>
       <c r="J37" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K37" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="38">
@@ -1777,7 +1777,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K39" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="40">
@@ -1812,7 +1812,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K40" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="41">
@@ -1847,7 +1847,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K41" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="42">
@@ -1917,7 +1917,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K43" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="44">
@@ -1949,10 +1949,10 @@
         <v>60.0%</v>
       </c>
       <c r="J44" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K44" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="45">
@@ -1984,10 +1984,10 @@
         <v>60.0%</v>
       </c>
       <c r="J45" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K45" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="46">
@@ -2022,7 +2022,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K46" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="47">
@@ -2054,10 +2054,10 @@
         <v>40.0%</v>
       </c>
       <c r="J47" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K47" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="48">
@@ -2127,7 +2127,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K49" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="50">
@@ -2162,7 +2162,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K50" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="51">
@@ -2197,7 +2197,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K51" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="52">
@@ -2267,7 +2267,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K53" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="54">
@@ -2299,10 +2299,10 @@
         <v>60.0%</v>
       </c>
       <c r="J54" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K54" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="55">
@@ -2334,10 +2334,10 @@
         <v>60.0%</v>
       </c>
       <c r="J55" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K55" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="56">
@@ -2372,7 +2372,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K56" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="57">
@@ -2404,10 +2404,10 @@
         <v>20.0%</v>
       </c>
       <c r="J57" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K57" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="58">
@@ -2477,7 +2477,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K59" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="60">
@@ -2512,7 +2512,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K60" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="61">
@@ -2547,7 +2547,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K61" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="62">
@@ -2617,7 +2617,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K63" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="64">
@@ -2649,10 +2649,10 @@
         <v>40.0%</v>
       </c>
       <c r="J64" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K64" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="65">
@@ -2684,10 +2684,10 @@
         <v>60.0%</v>
       </c>
       <c r="J65" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K65" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="66">
@@ -2722,7 +2722,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K66" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="67">
@@ -2754,10 +2754,10 @@
         <v>40.0%</v>
       </c>
       <c r="J67" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K67" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="68">
@@ -2827,7 +2827,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K69" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="70">
@@ -2862,7 +2862,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K70" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="71">
@@ -2897,7 +2897,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K71" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="72">
@@ -2967,7 +2967,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K73" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="74">
@@ -2999,10 +2999,10 @@
         <v>60.0%</v>
       </c>
       <c r="J74" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K74" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="75">
@@ -3034,10 +3034,10 @@
         <v>40.0%</v>
       </c>
       <c r="J75" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K75" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="76">
@@ -3072,7 +3072,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K76" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="77">
@@ -3104,10 +3104,10 @@
         <v>60.0%</v>
       </c>
       <c r="J77" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K77" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="78">
@@ -3177,7 +3177,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K79" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="80">
@@ -3212,7 +3212,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K80" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="81">
@@ -3247,7 +3247,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K81" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="82">
@@ -3317,7 +3317,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K83" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="84">
@@ -3349,10 +3349,10 @@
         <v>80.0%</v>
       </c>
       <c r="J84" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K84" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="85">
@@ -3384,10 +3384,10 @@
         <v>80.0%</v>
       </c>
       <c r="J85" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K85" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="86">
@@ -3422,7 +3422,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K86" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="87">
@@ -3454,10 +3454,10 @@
         <v>80.0%</v>
       </c>
       <c r="J87" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K87" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="88">
@@ -3527,7 +3527,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K89" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="90">
@@ -3562,7 +3562,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K90" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="91">
@@ -3597,7 +3597,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K91" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="92">
@@ -3667,7 +3667,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K93" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="94">
@@ -3699,10 +3699,10 @@
         <v>60.0%</v>
       </c>
       <c r="J94" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K94" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="95">
@@ -3734,10 +3734,10 @@
         <v>80.0%</v>
       </c>
       <c r="J95" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K95" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="96">
@@ -3772,7 +3772,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K96" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="97">
@@ -3804,10 +3804,10 @@
         <v>80.0%</v>
       </c>
       <c r="J97" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K97" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="98">
@@ -3877,7 +3877,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K99" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="100">
@@ -3912,7 +3912,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K100" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="101">
@@ -3947,7 +3947,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K101" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="102">
@@ -4017,7 +4017,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K103" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="104">
@@ -4049,10 +4049,10 @@
         <v>40.0%</v>
       </c>
       <c r="J104" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K104" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="105">
@@ -4084,10 +4084,10 @@
         <v>60.0%</v>
       </c>
       <c r="J105" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K105" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="106">
@@ -4122,7 +4122,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K106" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="107">
@@ -4154,10 +4154,10 @@
         <v>20.0%</v>
       </c>
       <c r="J107" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K107" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="108">
@@ -4227,7 +4227,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K109" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="110">
@@ -4262,7 +4262,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K110" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="111">
@@ -4297,7 +4297,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K111" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="112">
@@ -4367,7 +4367,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K113" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="114">
@@ -4399,10 +4399,10 @@
         <v>80.0%</v>
       </c>
       <c r="J114" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K114" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="115">
@@ -4434,10 +4434,10 @@
         <v>80.0%</v>
       </c>
       <c r="J115" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K115" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="116">
@@ -4472,7 +4472,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K116" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="117">
@@ -4504,10 +4504,10 @@
         <v>60.0%</v>
       </c>
       <c r="J117" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K117" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="118">
@@ -4577,7 +4577,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K119" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="120">
@@ -4612,7 +4612,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K120" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="121">
@@ -4647,7 +4647,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K121" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="122">
@@ -4717,7 +4717,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K123" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="124">
@@ -4749,10 +4749,10 @@
         <v>40.0%</v>
       </c>
       <c r="J124" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K124" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="125">
@@ -4784,10 +4784,10 @@
         <v>40.0%</v>
       </c>
       <c r="J125" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K125" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="126">
@@ -4822,7 +4822,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K126" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="127">
@@ -4854,10 +4854,10 @@
         <v>0.0%</v>
       </c>
       <c r="J127" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K127" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="128">
@@ -4927,7 +4927,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K129" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="130">
@@ -4962,7 +4962,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K130" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="131">
@@ -4997,7 +4997,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K131" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="132">
@@ -5067,7 +5067,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K133" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="134">
@@ -5099,10 +5099,10 @@
         <v>20.0%</v>
       </c>
       <c r="J134" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K134" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="135">
@@ -5134,10 +5134,10 @@
         <v>20.0%</v>
       </c>
       <c r="J135" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K135" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="136">
@@ -5172,7 +5172,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K136" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="137">
@@ -5204,10 +5204,10 @@
         <v>20.0%</v>
       </c>
       <c r="J137" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K137" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="138">
@@ -5277,7 +5277,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K139" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="140">
@@ -5312,7 +5312,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K140" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="141">
@@ -5347,7 +5347,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K141" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="142">
@@ -5417,7 +5417,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K143" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="144">
@@ -5449,10 +5449,10 @@
         <v>60.0%</v>
       </c>
       <c r="J144" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K144" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="145">
@@ -5484,10 +5484,10 @@
         <v>60.0%</v>
       </c>
       <c r="J145" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K145" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="146">
@@ -5522,7 +5522,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K146" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="147">
@@ -5554,10 +5554,10 @@
         <v>60.0%</v>
       </c>
       <c r="J147" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K147" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="148">
@@ -5627,7 +5627,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K149" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="150">
@@ -5662,7 +5662,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K150" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="151">
@@ -5697,7 +5697,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K151" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="152">
@@ -5767,7 +5767,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K153" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="154">
@@ -5799,10 +5799,10 @@
         <v>60.0%</v>
       </c>
       <c r="J154" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K154" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="155">
@@ -5834,10 +5834,10 @@
         <v>40.0%</v>
       </c>
       <c r="J155" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K155" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="156">
@@ -5872,7 +5872,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K156" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="157">
@@ -5904,10 +5904,10 @@
         <v>20.0%</v>
       </c>
       <c r="J157" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K157" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="158">
@@ -5977,7 +5977,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K159" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="160">
@@ -6012,7 +6012,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K160" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="161">
@@ -6047,7 +6047,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K161" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="162">
@@ -6117,7 +6117,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K163" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="164">
@@ -6149,10 +6149,10 @@
         <v>40.0%</v>
       </c>
       <c r="J164" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K164" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="165">
@@ -6184,10 +6184,10 @@
         <v>60.0%</v>
       </c>
       <c r="J165" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K165" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="166">
@@ -6222,7 +6222,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K166" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="167">
@@ -6254,10 +6254,10 @@
         <v>60.0%</v>
       </c>
       <c r="J167" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K167" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="168">
@@ -6327,7 +6327,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K169" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="170">
@@ -6362,7 +6362,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K170" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="171">
@@ -6397,7 +6397,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K171" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="172">
@@ -6467,7 +6467,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K173" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="174">
@@ -6499,10 +6499,10 @@
         <v>60.0%</v>
       </c>
       <c r="J174" t="str">
-        <v>44, 42, 25, 21, 23, 10, 29, 30, 17, 45</v>
+        <v>42, 29, 13, 50, 10, 25, 17, 19, 44, 45</v>
       </c>
       <c r="K174" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="175">
@@ -6534,10 +6534,10 @@
         <v>60.0%</v>
       </c>
       <c r="J175" t="str">
-        <v>29, 35, 7, 27, 21, 23, 10, 30, 45, 19</v>
+        <v>29, 28, 35, 7, 9, 10, 19, 45, 21, 23</v>
       </c>
       <c r="K175" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="176">
@@ -6572,7 +6572,7 @@
         <v>48, 9, 17, 40, 22, 42, 13, 6, 11, 37</v>
       </c>
       <c r="K176" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="177">
@@ -6604,10 +6604,10 @@
         <v>40.0%</v>
       </c>
       <c r="J177" t="str">
-        <v>10, 45, 23, 35, 29, 30, 42, 21, 44, 50</v>
+        <v>10, 45, 23, 35, 29, 30, 42, 9, 21, 44</v>
       </c>
       <c r="K177" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="178">
@@ -6677,7 +6677,7 @@
         <v>21, 35, 30, 45, 9, 42, 10, 20, 28, 36</v>
       </c>
       <c r="K179" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
     <row r="180">
@@ -6712,7 +6712,7 @@
         <v>35, 13, 17, 21, 24, 50, 7, 14, 23, 19</v>
       </c>
       <c r="K180" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="181">
@@ -6747,7 +6747,7 @@
         <v>33, 15, 24, 11, 10, 23, 26, 40, 50, 1</v>
       </c>
       <c r="K181" t="str">
-        <v>01/01/2026, 18:23:39</v>
+        <v>01/01/2026, 19:08:48</v>
       </c>
     </row>
     <row r="182">
@@ -6817,7 +6817,7 @@
         <v>29, 44, 9, 21, 35, 8, 34, 20, 22, 30</v>
       </c>
       <c r="K183" t="str">
-        <v>01/01/2026, 18:23:40</v>
+        <v>01/01/2026, 19:08:49</v>
       </c>
     </row>
   </sheetData>
